--- a/assets/constructions/examples/ctd_bs_adapter1.xlsx
+++ b/assets/constructions/examples/ctd_bs_adapter1.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ctd" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="ctd" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y6"/>
+  <dimension ref="A1:AC6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -554,11 +554,31 @@
           <t>releasepack</t>
         </is>
       </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>lcs</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>pricecurrency</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>pricevalue_rub</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DCK7-7-105</t>
+          <t>DCK6-3-56</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -568,20 +588,24 @@
       </c>
       <c r="C2" t="inlineStr"/>
       <c r="D2" t="n">
-        <v>46</v>
+        <v>36</v>
       </c>
       <c r="E2" t="n">
-        <v>46</v>
+        <v>18</v>
       </c>
       <c r="F2" t="n">
-        <v>90</v>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
+        <v>31</v>
+      </c>
+      <c r="G2" t="n">
+        <v>64</v>
+      </c>
+      <c r="H2" t="n">
+        <v>39</v>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr"/>
       <c r="K2" t="n">
-        <v>105</v>
+        <v>56</v>
       </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="n">
@@ -591,12 +615,12 @@
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>DER_DCK:7</t>
+          <t>DER_DCK:6</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>DER_DCK:7</t>
+          <t>DER_DCK:3</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -611,7 +635,7 @@
       <c r="U2" t="inlineStr"/>
       <c r="V2" t="inlineStr"/>
       <c r="W2" t="n">
-        <v>5.28</v>
+        <v>0.7</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -620,12 +644,26 @@
         <is>
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
         </is>
+      </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>81.54000000000001</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC2" t="n">
+        <v>6684.15</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>DCK5-3-47</t>
+          <t>DCK6-6-60</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -635,24 +673,20 @@
       </c>
       <c r="C3" t="inlineStr"/>
       <c r="D3" t="n">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="E3" t="n">
-        <v>18</v>
+        <v>36</v>
       </c>
       <c r="F3" t="n">
-        <v>31</v>
-      </c>
-      <c r="G3" t="n">
-        <v>50</v>
-      </c>
-      <c r="H3" t="n">
-        <v>29</v>
-      </c>
+        <v>64</v>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="n">
-        <v>47</v>
+        <v>60</v>
       </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="n">
@@ -662,12 +696,12 @@
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>DER_DCK:5</t>
+          <t>DER_DCK:6</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>DER_DCK:3</t>
+          <t>DER_DCK:6</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
@@ -682,7 +716,7 @@
       <c r="U3" t="inlineStr"/>
       <c r="V3" t="inlineStr"/>
       <c r="W3" t="n">
-        <v>0.46</v>
+        <v>1.46</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -691,12 +725,26 @@
         <is>
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
         </is>
+      </c>
+      <c r="Z3" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC3" t="n">
+        <v>5275.02</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>DCK4-2-50</t>
+          <t>DCK4-4-45</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -709,21 +757,17 @@
         <v>22</v>
       </c>
       <c r="E4" t="n">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="F4" t="n">
-        <v>24</v>
-      </c>
-      <c r="G4" t="n">
         <v>39</v>
       </c>
-      <c r="H4" t="n">
-        <v>36</v>
-      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
       <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr"/>
       <c r="K4" t="n">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="n">
@@ -738,7 +782,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>DER_DCK:2</t>
+          <t>DER_DCK:4</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>
@@ -753,7 +797,7 @@
       <c r="U4" t="inlineStr"/>
       <c r="V4" t="inlineStr"/>
       <c r="W4" t="n">
-        <v>0.22</v>
+        <v>0.29</v>
       </c>
       <c r="X4" t="n">
         <v>0</v>
@@ -762,12 +806,26 @@
         <is>
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
         </is>
+      </c>
+      <c r="Z4" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>64.34999999999999</v>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC4" t="n">
+        <v>5275.02</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>DCK6-3-96</t>
+          <t>DCK6-4-51</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -780,21 +838,21 @@
         <v>36</v>
       </c>
       <c r="E5" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="F5" t="n">
-        <v>31</v>
+        <v>39</v>
       </c>
       <c r="G5" t="n">
         <v>64</v>
       </c>
       <c r="H5" t="n">
-        <v>79</v>
+        <v>35</v>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
       <c r="K5" t="n">
-        <v>96</v>
+        <v>51</v>
       </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="n">
@@ -809,7 +867,7 @@
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>DER_DCK:3</t>
+          <t>DER_DCK:4</t>
         </is>
       </c>
       <c r="R5" t="inlineStr"/>
@@ -824,7 +882,7 @@
       <c r="U5" t="inlineStr"/>
       <c r="V5" t="inlineStr"/>
       <c r="W5" t="n">
-        <v>0.91</v>
+        <v>0.76</v>
       </c>
       <c r="X5" t="n">
         <v>0</v>
@@ -833,12 +891,26 @@
         <is>
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
         </is>
+      </c>
+      <c r="Z5" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA5" t="n">
+        <v>81.54000000000001</v>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC5" t="n">
+        <v>6684.15</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DCK6-2-63</t>
+          <t>DCK2-2-30</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -848,7 +920,7 @@
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="n">
-        <v>36</v>
+        <v>14</v>
       </c>
       <c r="E6" t="n">
         <v>14</v>
@@ -856,16 +928,12 @@
       <c r="F6" t="n">
         <v>24</v>
       </c>
-      <c r="G6" t="n">
-        <v>64</v>
-      </c>
-      <c r="H6" t="n">
-        <v>45</v>
-      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr"/>
       <c r="K6" t="n">
-        <v>63</v>
+        <v>30</v>
       </c>
       <c r="L6" t="inlineStr"/>
       <c r="M6" t="n">
@@ -875,7 +943,7 @@
       <c r="O6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>DER_DCK:6</t>
+          <t>DER_DCK:2</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -895,7 +963,7 @@
       <c r="U6" t="inlineStr"/>
       <c r="V6" t="inlineStr"/>
       <c r="W6" t="n">
-        <v>0.66</v>
+        <v>0.09</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -904,6 +972,20 @@
         <is>
           <t>2019 / DEREK Металлорежущий инструмент и оснастка 2019 RUS</t>
         </is>
+      </c>
+      <c r="Z6" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>53.64</v>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>USD</t>
+        </is>
+      </c>
+      <c r="AC6" t="n">
+        <v>4397.08</v>
       </c>
     </row>
   </sheetData>
